--- a/SqueezeReviews.xlsx
+++ b/SqueezeReviews.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10920"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rmazorow/Documents/Squeeze-Threshold-Verification/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2140BFED-84A7-5A40-BF29-9434D9676C3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B98BF45-0F5C-3B47-8F4B-09CE41111AC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980"/>
   </bookViews>
   <sheets>
     <sheet name="R01" sheetId="5" r:id="rId1"/>
     <sheet name="R02" sheetId="4" r:id="rId2"/>
     <sheet name="R03" sheetId="1" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" fullCalcOnLoad="true"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -38,16 +38,100 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="94" uniqueCount="29">
   <si>
     <t>R02</t>
+  </si>
+  <si>
+    <t>SubID</t>
+  </si>
+  <si>
+    <t>Block</t>
+  </si>
+  <si>
+    <t>S_01</t>
+  </si>
+  <si>
+    <t>Trial</t>
+  </si>
+  <si>
+    <t>ReachEnd</t>
+  </si>
+  <si>
+    <t>StabilStart</t>
+  </si>
+  <si>
+    <t>CorrStart</t>
+  </si>
+  <si>
+    <t>RevLabel</t>
+  </si>
+  <si>
+    <t>G</t>
+  </si>
+  <si>
+    <t>FilePath</t>
+  </si>
+  <si>
+    <t>Camera</t>
+  </si>
+  <si>
+    <t>opti</t>
+  </si>
+  <si>
+    <t>WTest1/S_01/_trial001_2026-04-14_13-26-41.mat</t>
+  </si>
+  <si>
+    <t>WTest1/S_01/_trial002_2026-04-14_13-27-11.mat</t>
+  </si>
+  <si>
+    <t>WTest1/S_01/_trial003_2026-04-14_13-27-41.mat</t>
+  </si>
+  <si>
+    <t>WTest1/S_01/_trial004_2026-04-14_13-28-49.mat</t>
+  </si>
+  <si>
+    <t>WTest1/S_01/_trial005_2026-04-14_13-29-25.mat</t>
+  </si>
+  <si>
+    <t>WTest1</t>
+  </si>
+  <si>
+    <t>WTest2</t>
+  </si>
+  <si>
+    <t>WTest3</t>
+  </si>
+  <si>
+    <t>WTest4</t>
+  </si>
+  <si>
+    <t>WTest5</t>
+  </si>
+  <si>
+    <t>S_02</t>
+  </si>
+  <si>
+    <t>WTest1/S_02/_trial001_2026-04-28_16-31-08.mat</t>
+  </si>
+  <si>
+    <t>WTest1/S_02/_trial002_2026-04-28_16-31-27.mat</t>
+  </si>
+  <si>
+    <t>WTest1/S_02/_trial003_2026-04-28_16-31-47.mat</t>
+  </si>
+  <si>
+    <t>WTest1/S_02/_trial004_2026-04-28_16-32-10.mat</t>
+  </si>
+  <si>
+    <t>WTest1/S_02/_trial005_2026-04-28_16-32-32.mat</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <fonts count="3">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -62,6 +146,12 @@
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -71,7 +161,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -79,13 +169,15 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="true"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -104,7 +196,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -255,7 +347,7 @@
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill rotWithShape="true">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -279,9 +371,9 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="5400000" scaled="false"/>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill rotWithShape="true">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -305,7 +397,7 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="5400000" scaled="false"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -340,7 +432,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="false">
               <a:srgbClr val="000000">
                 <a:alpha val="63000"/>
               </a:srgbClr>
@@ -358,7 +450,7 @@
             <a:satMod val="170000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill rotWithShape="true">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -383,7 +475,7 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="5400000" scaled="false"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
@@ -419,10 +511,342 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C9FC292-298F-7347-9E2B-E19B83CAC426}">
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C9FC292-298F-7347-9E2B-E19B83CAC426}">
+  <dimension ref="A1:I11"/>
+  <sheetFormatPr xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="7.7109375" customWidth="true"/>
+    <col min="2" max="2" width="6.7109375" customWidth="true"/>
+    <col min="4" max="4" width="9.7109375" customWidth="true"/>
+    <col min="5" max="5" width="12.7109375" customWidth="true"/>
+    <col min="6" max="6" width="10.7109375" customWidth="true"/>
+    <col min="7" max="7" width="9.7109375" customWidth="true"/>
+    <col min="8" max="8" width="46.7109375" customWidth="true"/>
+    <col min="9" max="9" width="7.7109375" customWidth="true"/>
+    <col min="3" max="3" width="6.7109375" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="0" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="0" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="F1" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="G1" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="H1" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="I1" s="0" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="2" x14ac:dyDescent="0.2">
+      <c r="A2" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="0">
+        <v>1</v>
+      </c>
+      <c r="D2" s="0">
+        <v>1423</v>
+      </c>
+      <c r="E2" s="0">
+        <v>1495</v>
+      </c>
+      <c r="F2" s="0">
+        <v>1896</v>
+      </c>
+      <c r="G2" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="H2" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="I2" s="0" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="3" x14ac:dyDescent="0.2">
+      <c r="A3" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3" s="0">
+        <v>2344</v>
+      </c>
+      <c r="E3" s="0">
+        <v>2427</v>
+      </c>
+      <c r="F3" s="0">
+        <v>2828</v>
+      </c>
+      <c r="G3" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="H3" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="I3" s="0" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="4" x14ac:dyDescent="0.2">
+      <c r="A4" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="0">
+        <v>3</v>
+      </c>
+      <c r="D4" s="0">
+        <v>3354</v>
+      </c>
+      <c r="E4" s="0">
+        <v>3435</v>
+      </c>
+      <c r="F4" s="0">
+        <v>3836</v>
+      </c>
+      <c r="G4" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="H4" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="I4" s="0" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="5" x14ac:dyDescent="0.2">
+      <c r="A5" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" s="0">
+        <v>4</v>
+      </c>
+      <c r="D5" s="0">
+        <v>1365</v>
+      </c>
+      <c r="E5" s="0">
+        <v>1437</v>
+      </c>
+      <c r="F5" s="0">
+        <v>1838</v>
+      </c>
+      <c r="G5" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="H5" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="I5" s="0" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="6" x14ac:dyDescent="0.2">
+      <c r="A6" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6" s="0">
+        <v>5</v>
+      </c>
+      <c r="D6" s="0">
+        <v>1556</v>
+      </c>
+      <c r="E6" s="0">
+        <v>1630</v>
+      </c>
+      <c r="F6" s="0">
+        <v>2031</v>
+      </c>
+      <c r="G6" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="H6" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="I6" s="0" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" s="0">
+        <v>1</v>
+      </c>
+      <c r="D7" s="0">
+        <v>1765</v>
+      </c>
+      <c r="E7" s="0">
+        <v>1817</v>
+      </c>
+      <c r="F7" s="0">
+        <v>2218</v>
+      </c>
+      <c r="G7" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="H7" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="I7" s="0" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" s="0">
+        <v>2</v>
+      </c>
+      <c r="D8" s="0">
+        <v>1663</v>
+      </c>
+      <c r="E8" s="0">
+        <v>1711</v>
+      </c>
+      <c r="F8" s="0">
+        <v>2112</v>
+      </c>
+      <c r="G8" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="H8" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="I8" s="0" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" s="0">
+        <v>3</v>
+      </c>
+      <c r="D9" s="0">
+        <v>2126</v>
+      </c>
+      <c r="E9" s="0">
+        <v>2184</v>
+      </c>
+      <c r="F9" s="0">
+        <v>2585</v>
+      </c>
+      <c r="G9" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="H9" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="I9" s="0" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="C10" s="0">
+        <v>4</v>
+      </c>
+      <c r="D10" s="0">
+        <v>1929</v>
+      </c>
+      <c r="E10" s="0">
+        <v>1982</v>
+      </c>
+      <c r="F10" s="0">
+        <v>2383</v>
+      </c>
+      <c r="G10" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="H10" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="I10" s="0" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" s="0">
+        <v>5</v>
+      </c>
+      <c r="D11" s="0">
+        <v>1515</v>
+      </c>
+      <c r="E11" s="0">
+        <v>1551</v>
+      </c>
+      <c r="F11" s="0">
+        <v>1952</v>
+      </c>
+      <c r="G11" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="H11" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="I11" s="0" t="s">
+        <v>12</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/SqueezeReviews.xlsx
+++ b/SqueezeReviews.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rmazorow/Documents/Squeeze-Threshold-Verification/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B98BF45-0F5C-3B47-8F4B-09CE41111AC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9711BD43-F14E-9849-953C-ECC784B21D7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="94" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="29" uniqueCount="17">
   <si>
     <t>R02</t>
   </si>
@@ -46,6 +46,9 @@
     <t>SubID</t>
   </si>
   <si>
+    <t>WTest1</t>
+  </si>
+  <si>
     <t>Block</t>
   </si>
   <si>
@@ -73,12 +76,6 @@
     <t>FilePath</t>
   </si>
   <si>
-    <t>Camera</t>
-  </si>
-  <si>
-    <t>opti</t>
-  </si>
-  <si>
     <t>WTest1/S_01/_trial001_2026-04-14_13-26-41.mat</t>
   </si>
   <si>
@@ -92,39 +89,6 @@
   </si>
   <si>
     <t>WTest1/S_01/_trial005_2026-04-14_13-29-25.mat</t>
-  </si>
-  <si>
-    <t>WTest1</t>
-  </si>
-  <si>
-    <t>WTest2</t>
-  </si>
-  <si>
-    <t>WTest3</t>
-  </si>
-  <si>
-    <t>WTest4</t>
-  </si>
-  <si>
-    <t>WTest5</t>
-  </si>
-  <si>
-    <t>S_02</t>
-  </si>
-  <si>
-    <t>WTest1/S_02/_trial001_2026-04-28_16-31-08.mat</t>
-  </si>
-  <si>
-    <t>WTest1/S_02/_trial002_2026-04-28_16-31-27.mat</t>
-  </si>
-  <si>
-    <t>WTest1/S_02/_trial003_2026-04-28_16-31-47.mat</t>
-  </si>
-  <si>
-    <t>WTest1/S_02/_trial004_2026-04-28_16-32-10.mat</t>
-  </si>
-  <si>
-    <t>WTest1/S_02/_trial005_2026-04-28_16-32-32.mat</t>
   </si>
 </sst>
 </file>
@@ -512,7 +476,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C9FC292-298F-7347-9E2B-E19B83CAC426}">
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" customWidth="true"/>
@@ -522,45 +486,42 @@
     <col min="6" max="6" width="10.7109375" customWidth="true"/>
     <col min="7" max="7" width="9.7109375" customWidth="true"/>
     <col min="8" max="8" width="46.7109375" customWidth="true"/>
-    <col min="9" max="9" width="7.7109375" customWidth="true"/>
+    <col min="9" max="9" width="7.6640625" customWidth="true"/>
     <col min="3" max="3" width="6.7109375" customWidth="true"/>
   </cols>
   <sheetData>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="1" x14ac:dyDescent="0.2">
+    <row r="1">
       <c r="A1" s="0" t="s">
         <v>1</v>
       </c>
       <c r="B1" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="0" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="0" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="0" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="B2" s="0" t="s">
         <v>4</v>
-      </c>
-      <c r="D1" s="0" t="s">
-        <v>5</v>
-      </c>
-      <c r="E1" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="F1" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="G1" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="H1" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="I1" s="0" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="2" x14ac:dyDescent="0.2">
-      <c r="A2" s="0" t="s">
-        <v>18</v>
-      </c>
-      <c r="B2" s="0" t="s">
-        <v>3</v>
       </c>
       <c r="C2" s="0">
         <v>1</v>
@@ -575,21 +536,18 @@
         <v>1896</v>
       </c>
       <c r="G2" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H2" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="I2" s="0" t="s">
         <v>12</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="3" x14ac:dyDescent="0.2">
+    <row r="3">
       <c r="A3" s="0" t="s">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C3" s="0">
         <v>2</v>
@@ -604,21 +562,18 @@
         <v>2828</v>
       </c>
       <c r="G3" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H3" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="I3" s="0" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="4" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4">
       <c r="A4" s="0" t="s">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C4" s="0">
         <v>3</v>
@@ -633,21 +588,18 @@
         <v>3836</v>
       </c>
       <c r="G4" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H4" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="I4" s="0" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="5" x14ac:dyDescent="0.2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5">
       <c r="A5" s="0" t="s">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C5" s="0">
         <v>4</v>
@@ -662,21 +614,18 @@
         <v>1838</v>
       </c>
       <c r="G5" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H5" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="I5" s="0" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="6" x14ac:dyDescent="0.2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6">
       <c r="A6" s="0" t="s">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C6" s="0">
         <v>5</v>
@@ -691,158 +640,10 @@
         <v>2031</v>
       </c>
       <c r="G6" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H6" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="I6" s="0" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="0" t="s">
-        <v>18</v>
-      </c>
-      <c r="B7" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="C7" s="0">
-        <v>1</v>
-      </c>
-      <c r="D7" s="0">
-        <v>1765</v>
-      </c>
-      <c r="E7" s="0">
-        <v>1817</v>
-      </c>
-      <c r="F7" s="0">
-        <v>2218</v>
-      </c>
-      <c r="G7" s="0" t="s">
-        <v>9</v>
-      </c>
-      <c r="H7" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="I7" s="0" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="0" t="s">
-        <v>18</v>
-      </c>
-      <c r="B8" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="C8" s="0">
-        <v>2</v>
-      </c>
-      <c r="D8" s="0">
-        <v>1663</v>
-      </c>
-      <c r="E8" s="0">
-        <v>1711</v>
-      </c>
-      <c r="F8" s="0">
-        <v>2112</v>
-      </c>
-      <c r="G8" s="0" t="s">
-        <v>9</v>
-      </c>
-      <c r="H8" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="I8" s="0" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="0" t="s">
-        <v>18</v>
-      </c>
-      <c r="B9" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="C9" s="0">
-        <v>3</v>
-      </c>
-      <c r="D9" s="0">
-        <v>2126</v>
-      </c>
-      <c r="E9" s="0">
-        <v>2184</v>
-      </c>
-      <c r="F9" s="0">
-        <v>2585</v>
-      </c>
-      <c r="G9" s="0" t="s">
-        <v>9</v>
-      </c>
-      <c r="H9" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="I9" s="0" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="0" t="s">
-        <v>18</v>
-      </c>
-      <c r="B10" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="C10" s="0">
-        <v>4</v>
-      </c>
-      <c r="D10" s="0">
-        <v>1929</v>
-      </c>
-      <c r="E10" s="0">
-        <v>1982</v>
-      </c>
-      <c r="F10" s="0">
-        <v>2383</v>
-      </c>
-      <c r="G10" s="0" t="s">
-        <v>9</v>
-      </c>
-      <c r="H10" s="0" t="s">
-        <v>27</v>
-      </c>
-      <c r="I10" s="0" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="0" t="s">
-        <v>18</v>
-      </c>
-      <c r="B11" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="C11" s="0">
-        <v>5</v>
-      </c>
-      <c r="D11" s="0">
-        <v>1515</v>
-      </c>
-      <c r="E11" s="0">
-        <v>1551</v>
-      </c>
-      <c r="F11" s="0">
-        <v>1952</v>
-      </c>
-      <c r="G11" s="0" t="s">
-        <v>9</v>
-      </c>
-      <c r="H11" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="I11" s="0" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
